--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Atividade - Escore.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Atividade - Escore.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elios\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1F2C34-2597-45DD-9759-4AC8CFE1339E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798CF9DF-B49D-4B73-8B55-2466FF7FE67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sexo" sheetId="3" r:id="rId1"/>
@@ -18,11 +18,16 @@
     <sheet name="tempo de acesso" sheetId="5" r:id="rId3"/>
     <sheet name="Amostra" sheetId="2" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">Amostra!$C$2:$C$31</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Amostra!$C$2:$C$31</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Amostra!$B$2:$B$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
-    <pivotCache cacheId="16" r:id="rId6"/>
-    <pivotCache cacheId="25" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="2" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -63,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="42">
   <si>
     <t>Tempo de acesso semanal</t>
   </si>
@@ -166,11 +171,39 @@
   <si>
     <t>Desvio Padrão</t>
   </si>
+  <si>
+    <t>Coef. De Variação</t>
+  </si>
+  <si>
+    <t>Mínimo</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Máximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escor 60</t>
+  </si>
+  <si>
+    <t>Outlier</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.000"/>
+  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -224,7 +257,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -265,11 +298,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -307,53 +393,37 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="45">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -425,6 +495,24 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1755,6 +1843,136 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Idade</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Idade</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{134A2AB8-9C81-4E61-8DDB-1845B9C34728}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Tempo de Acesso</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Tempo de Acesso</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{EE592058-5C4E-42C7-93C7-DDE7B166DBC4}">
+          <cx:dataLabels>
+            <cx:visibility seriesName="0" categoryName="0" value="1"/>
+          </cx:dataLabels>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:visibility meanLine="0" meanMarker="1" nonoutliers="0" outliers="1"/>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0" hidden="1">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1915,6 +2133,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3925,6 +4223,1036 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -4855,6 +6183,162 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>590742</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>4235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1150697</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>130465</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Gráfico 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E2E6285E-74EE-AFA4-CA3F-42DCC8BAEED4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2755515" y="6306129"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>32714</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>100446</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>25017</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>63115</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="Gráfico 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{42BE4C25-F5FA-0401-8025-408B9F01C855}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2803623" y="9182870"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5481,7 +6965,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8DB2F7D-7163-405E-9E66-F9DDA2FE6CDB}" name="Tabela dinâmica2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sexo">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E8DB2F7D-7163-405E-9E66-F9DDA2FE6CDB}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Sexo">
   <location ref="A3:D6" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" dataField="1" showAll="0">
@@ -5528,10 +7012,10 @@
     <dataField name="fac" fld="0" subtotal="count" showDataAs="runTotal" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="44">
+    <format dxfId="38">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="37">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5540,26 +7024,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="36">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="34">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="38">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -5570,26 +7054,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="30">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="28">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -5614,7 +7098,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4FB4F66-6C34-4ECE-87A4-EDF2E5329E65}" name="Tabela dinâmica4" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Idade">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4FB4F66-6C34-4ECE-87A4-EDF2E5329E65}" name="Tabela dinâmica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Idade">
   <location ref="A3:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -5698,22 +7182,22 @@
     <dataField name="fac" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="1"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="36">
+    <format dxfId="24">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="23">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="21">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -5724,7 +7208,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="18">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -5733,16 +7217,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="17">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="15">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="9">
@@ -5759,10 +7243,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -5787,7 +7271,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E00DA975-3257-4A11-9629-C00D632D610A}" name="Tabela dinâmica6" cacheId="25" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Acesso">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E00DA975-3257-4A11-9629-C00D632D610A}" name="Tabela dinâmica6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Acesso">
   <location ref="A3:D14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -5878,16 +7362,16 @@
     <dataField name="fac" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="1"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="23">
+    <format dxfId="11">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="10">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="9">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="8">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="10">
@@ -5905,10 +7389,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="7">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="6">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -5919,16 +7403,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="5">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="4">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="3">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="10">
@@ -5946,10 +7430,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -6271,15 +7755,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B15838B8-3648-4515-90BE-A5C129E971C2}">
   <dimension ref="A3:D11"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -6293,7 +7777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
@@ -6307,7 +7791,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>4</v>
       </c>
@@ -6321,7 +7805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>5</v>
       </c>
@@ -6333,7 +7817,7 @@
       </c>
       <c r="D6" s="10"/>
     </row>
-    <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>3</v>
       </c>
@@ -6341,7 +7825,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>2</v>
       </c>
@@ -6349,7 +7833,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>4</v>
       </c>
@@ -6357,7 +7841,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
         <v>5</v>
       </c>
@@ -6374,15 +7858,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09C8D099-9DFA-41B4-8055-E627740A3DB2}">
   <dimension ref="A3:D26"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
@@ -6396,7 +7880,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>9</v>
       </c>
@@ -6410,7 +7894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
@@ -6424,7 +7908,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
@@ -6438,7 +7922,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>12</v>
       </c>
@@ -6452,7 +7936,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>13</v>
       </c>
@@ -6466,7 +7950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>14</v>
       </c>
@@ -6480,7 +7964,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -6494,7 +7978,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>16</v>
       </c>
@@ -6508,7 +7992,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>17</v>
       </c>
@@ -6522,7 +8006,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>5</v>
       </c>
@@ -6534,7 +8018,7 @@
       </c>
       <c r="D13" s="10"/>
     </row>
-    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>1</v>
       </c>
@@ -6542,7 +8026,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>9</v>
       </c>
@@ -6550,7 +8034,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>10</v>
       </c>
@@ -6558,7 +8042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>11</v>
       </c>
@@ -6566,7 +8050,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>12</v>
       </c>
@@ -6574,7 +8058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>13</v>
       </c>
@@ -6582,7 +8066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>14</v>
       </c>
@@ -6590,7 +8074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>15</v>
       </c>
@@ -6598,7 +8082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>16</v>
       </c>
@@ -6606,7 +8090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>17</v>
       </c>
@@ -6614,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
         <v>5</v>
       </c>
@@ -6631,15 +8115,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D724076-AD36-435B-94E8-134FD66284AC}">
   <dimension ref="A3:D27"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>18</v>
       </c>
@@ -6653,7 +8137,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
@@ -6667,7 +8151,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
@@ -6681,7 +8165,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -6695,7 +8179,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
@@ -6709,7 +8193,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
@@ -6723,7 +8207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
@@ -6737,7 +8221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
@@ -6751,7 +8235,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
@@ -6765,7 +8249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>27</v>
       </c>
@@ -6779,7 +8263,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>28</v>
       </c>
@@ -6793,7 +8277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>5</v>
       </c>
@@ -6805,7 +8289,7 @@
       </c>
       <c r="D14" s="10"/>
     </row>
-    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>18</v>
       </c>
@@ -6813,7 +8297,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>19</v>
       </c>
@@ -6821,7 +8305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>20</v>
       </c>
@@ -6829,7 +8313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>21</v>
       </c>
@@ -6837,7 +8321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>22</v>
       </c>
@@ -6845,7 +8329,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>23</v>
       </c>
@@ -6853,7 +8337,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
         <v>24</v>
       </c>
@@ -6861,7 +8345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
         <v>25</v>
       </c>
@@ -6869,7 +8353,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="9" t="s">
         <v>26</v>
       </c>
@@ -6877,7 +8361,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="9" t="s">
         <v>27</v>
       </c>
@@ -6885,7 +8369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="9" t="s">
         <v>28</v>
       </c>
@@ -6893,7 +8377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
         <v>5</v>
       </c>
@@ -6909,15 +8393,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G36"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.26953125" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" customWidth="1"/>
-    <col min="6" max="8" width="17.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="8" width="17.5703125" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -6929,7 +8415,7 @@
       </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -6940,7 +8426,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -6951,7 +8437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -6962,7 +8448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
@@ -6973,7 +8459,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
@@ -6984,7 +8470,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
@@ -6995,7 +8481,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
@@ -7006,7 +8492,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
@@ -7017,7 +8503,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>4</v>
       </c>
@@ -7028,7 +8514,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -7039,7 +8525,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2</v>
       </c>
@@ -7050,7 +8536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>4</v>
       </c>
@@ -7061,7 +8547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -7072,7 +8558,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
@@ -7085,7 +8571,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>2</v>
       </c>
@@ -7098,7 +8584,7 @@
       <c r="E16" s="6"/>
       <c r="F16" s="5"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>4</v>
       </c>
@@ -7111,7 +8597,7 @@
       <c r="E17" s="6"/>
       <c r="F17" s="5"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>4</v>
       </c>
@@ -7123,7 +8609,7 @@
       </c>
       <c r="F18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>2</v>
       </c>
@@ -7135,7 +8621,7 @@
       </c>
       <c r="F19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>2</v>
       </c>
@@ -7148,7 +8634,7 @@
       <c r="E20" s="6"/>
       <c r="F20" s="5"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>4</v>
       </c>
@@ -7161,7 +8647,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="5"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>4</v>
       </c>
@@ -7173,7 +8659,7 @@
       </c>
       <c r="F22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>4</v>
       </c>
@@ -7185,7 +8671,7 @@
       </c>
       <c r="F23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>2</v>
       </c>
@@ -7197,7 +8683,7 @@
       </c>
       <c r="F24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
@@ -7209,7 +8695,7 @@
       </c>
       <c r="F25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
@@ -7219,9 +8705,10 @@
       <c r="C26" s="2">
         <v>38</v>
       </c>
+      <c r="E26" s="15"/>
       <c r="F26" s="5"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2</v>
       </c>
@@ -7231,14 +8718,16 @@
       <c r="C27" s="2">
         <v>30</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="D27" s="21"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2</v>
       </c>
@@ -7248,19 +8737,19 @@
       <c r="C28" s="2">
         <v>44</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="17">
         <f>AVERAGE(B2:B31)</f>
         <v>23.333333333333332</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="17">
         <f>AVERAGE(C2:C31)</f>
         <v>33.033333333333331</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
@@ -7270,19 +8759,19 @@
       <c r="C29" s="2">
         <v>48</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="16" cm="1">
+      <c r="F29" s="17" cm="1">
         <f t="array" ref="F29:F31">_xlfn.MODE.MULT(B2:B31)</f>
         <v>13</v>
       </c>
-      <c r="G29" s="9" cm="1">
+      <c r="G29" s="18" cm="1">
         <f t="array" ref="G29">_xlfn.MODE.MULT(C2:C31)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2</v>
       </c>
@@ -7292,12 +8781,15 @@
       <c r="C30" s="2">
         <v>40</v>
       </c>
-      <c r="F30" s="16">
+      <c r="D30" s="21"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="17">
         <v>20</v>
       </c>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="15"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
@@ -7307,53 +8799,164 @@
       <c r="C31" s="2">
         <v>60</v>
       </c>
-      <c r="F31" s="16">
+      <c r="D31" s="21"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="17">
         <v>33</v>
       </c>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E32" s="15" t="s">
+      <c r="G31" s="25"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E32" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="17">
         <f>MEDIAN(B2:B31)</f>
         <v>20.5</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="18">
         <f>MEDIAN(C2:C31)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E33" s="15" t="s">
+    <row r="33" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E33" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="17">
         <f>_xlfn.VAR.S(B2:B31)</f>
         <v>76.16091954022987</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="17">
         <f>_xlfn.VAR.S(C2:C31)</f>
         <v>82.37816091954025</v>
       </c>
     </row>
-    <row r="34" spans="5:7" x14ac:dyDescent="0.25">
-      <c r="E34" s="15" t="s">
+    <row r="34" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E34" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="17">
         <f>_xlfn.STDEV.S(B2:B31)</f>
         <v>8.7270223753712166</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="17">
         <f>_xlfn.STDEV.S(C2:C31)</f>
         <v>9.0762415635294911</v>
       </c>
     </row>
-    <row r="36" spans="5:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="E35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="20">
+        <f>F34/(F28 * 100)</f>
+        <v>3.7401524465876649E-3</v>
+      </c>
+      <c r="G35" s="20">
+        <f>G34/(G28*100)</f>
+        <v>2.7476008769514101E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="5:11" x14ac:dyDescent="0.2">
       <c r="E36" s="6"/>
       <c r="F36" s="5"/>
+    </row>
+    <row r="38" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="J38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K38" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="J39" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K39" s="2">
+        <v>15.75</v>
+      </c>
+    </row>
+    <row r="40" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="J40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" s="2">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="41" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="J41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K41" s="2">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="42" spans="5:11" x14ac:dyDescent="0.2">
+      <c r="J42" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K42" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J55" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K55" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J56" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K56" s="2">
+        <v>26.75</v>
+      </c>
+    </row>
+    <row r="57" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K57" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K58" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J59" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K59" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="10:12" x14ac:dyDescent="0.2">
+      <c r="J61" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K61" s="26">
+        <f>STANDARDIZE(K59,G28,G34)</f>
+        <v>1.6489938662283201</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Faculdade/Terceiro Semestre/Estatística Aplicada/Atividade - Escore.xlsx
+++ b/Faculdade/Terceiro Semestre/Estatística Aplicada/Atividade - Escore.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aluno\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC373E0B-19B5-4548-AD8D-CE951F1BF656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01218C46-7DFD-4505-A270-3A71547A6B65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sexo" sheetId="3" r:id="rId1"/>
@@ -20,17 +20,25 @@
     <sheet name="Amostra" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Amostra!$B$2:$B$31</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Amostra!$C$2:$C$31</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">idade!$A$17:$A$25</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">idade!$B$16</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">idade!$B$17:$B$25</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">'tempo de acesso'!$A$17:$A$21</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">'tempo de acesso'!$A$17:$A$26</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">'tempo de acesso'!$B$16</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">'tempo de acesso'!$B$17:$B$21</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">'tempo de acesso'!$B$17:$B$26</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Amostra!$B$2:$B$31</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Amostra!$C$2:$C$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId6"/>
-    <pivotCache cacheId="1" r:id="rId7"/>
-    <pivotCache cacheId="2" r:id="rId8"/>
-    <pivotCache cacheId="11" r:id="rId9"/>
-    <pivotCache cacheId="21" r:id="rId10"/>
-    <pivotCache cacheId="31" r:id="rId11"/>
+    <pivotCache cacheId="6" r:id="rId7"/>
+    <pivotCache cacheId="7" r:id="rId8"/>
+    <pivotCache cacheId="3" r:id="rId9"/>
+    <pivotCache cacheId="4" r:id="rId10"/>
+    <pivotCache cacheId="5" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -71,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="65">
   <si>
     <t>Tempo de acesso semanal</t>
   </si>
@@ -128,36 +136,6 @@
   </si>
   <si>
     <t>Tempo de Acesso</t>
-  </si>
-  <si>
-    <t>20-22</t>
-  </si>
-  <si>
-    <t>23-25</t>
-  </si>
-  <si>
-    <t>26-28</t>
-  </si>
-  <si>
-    <t>29-31</t>
-  </si>
-  <si>
-    <t>32-34</t>
-  </si>
-  <si>
-    <t>35-37</t>
-  </si>
-  <si>
-    <t>38-40</t>
-  </si>
-  <si>
-    <t>44-46</t>
-  </si>
-  <si>
-    <t>47-49</t>
-  </si>
-  <si>
-    <t>59-61</t>
   </si>
   <si>
     <t>Média</t>
@@ -285,14 +263,23 @@
   <si>
     <t>Os indíviduos da faixa etária 12-16 são os mais novos e os indívidups da faixa etária 37-41 são os mais velhos. Os mais novos possuem um tempo menor de acesso semanal de 23,13 comparado aos mais velhos que possuem 49,33, os velhos passam muito mais tempo conectados do que os mais novos.</t>
   </si>
+  <si>
+    <t>20-29</t>
+  </si>
+  <si>
+    <t>30-39</t>
+  </si>
+  <si>
+    <t>40-49</t>
+  </si>
+  <si>
+    <t>50-60</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -465,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -523,9 +510,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -544,20 +528,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="92">
+  <dxfs count="102">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
     <dxf>
       <alignment vertical="center"/>
     </dxf>
@@ -688,36 +738,6 @@
       <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
       <alignment vertical="center"/>
     </dxf>
     <dxf>
@@ -731,12 +751,6 @@
     </dxf>
     <dxf>
       <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
     </dxf>
     <dxf>
       <alignment horizontal="center"/>
@@ -1459,696 +1473,6 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Idade</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>idade!$B$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>fi</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>idade!$A$17:$A$25</c:f>
-              <c:strCache>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>12-14</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>15-17</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>18-20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>21-23</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>24-26</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>30-32</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>33-35</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>36-38</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>39-41</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>idade!$B$17:$B$25</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-BA0A-46A6-9739-98392A837C55}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2103754960"/>
-        <c:axId val="2099317936"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2103754960"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2099317936"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2099317936"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2103754960"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="pt-BR"/>
-              <a:t>Tempo De acesso</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="pt-BR"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'tempo de acesso'!$B$16</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>fi</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>'tempo de acesso'!$A$17:$A$26</c:f>
-              <c:strCache>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>20-22</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>23-25</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>26-28</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>29-31</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32-34</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>35-37</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>38-40</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>44-46</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>47-49</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>59-61</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'tempo de acesso'!$B$17:$B$26</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7F0D-4E18-8FA3-9D9313895337}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="2003454768"/>
-        <c:axId val="2003455728"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="2003454768"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2003455728"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="2003455728"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="pt-BR"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2003454768"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="pt-BR"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="pt-BR"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[Atividade - Escore.xlsx]Parte 2!Tabela dinâmica2</c:name>
     <c:fmtId val="0"/>
@@ -2666,7 +1990,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -2727,49 +2051,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2802,7 +2084,6 @@
               <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2855,49 +2136,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2930,7 +2169,6 @@
               <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3180,7 +2418,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3399,7 +2636,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -3460,49 +2697,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3586,49 +2781,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4126,7 +3279,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
@@ -4570,8 +3723,180 @@
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.0</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Idade</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" compatLnSpc="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="0" lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Idade</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{1D163D19-46C5-4FE1-BC28-323D25DB012F}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>fi</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="2.19000006"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.6</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Tempo De acesso</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1" compatLnSpc="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:rPr kumimoji="0" lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0" noProof="0">
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:uLnTx/>
+              <a:uFillTx/>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Tempo De acesso</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{8DF23A07-69B9-47F2-A393-72ACD0A36571}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.5</cx:f>
+              <cx:v>fi</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="2.19000006"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/chartEx3.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -4631,12 +3956,12 @@
 </cx:chartSpace>
 </file>
 
-<file path=xl/charts/chartEx2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chartEx4.xml><?xml version="1.0" encoding="utf-8"?>
 <cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
   <cx:chartData>
     <cx:data id="0">
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.1</cx:f>
+        <cx:f>_xlchart.v1.9</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
@@ -10236,27 +9561,69 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{216CDE6B-6F44-FB2A-DC30-39A175FE6499}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{216CDE6B-6F44-FB2A-DC30-39A175FE6499}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3584575" y="1022350"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10277,27 +9644,69 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3205C495-5630-8E42-4F9B-A6CE38020E3F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Gráfico 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3205C495-5630-8E42-4F9B-A6CE38020E3F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3578225" y="1022350"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Este gráfico não está disponível na sua versão de Excel.
+Editar esta forma ou salvar esta pasta de trabalho em um formato de arquivo diferente quebrará o gráfico permanentemente.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10624,7 +10033,7 @@
             <a:rPr lang="pt-BR" sz="1200" baseline="0">
               <a:effectLst/>
             </a:rPr>
-            <a:t> : Quantitativa Discreta; </a:t>
+            <a:t> : Quantitativa Continua; </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="pt-BR" sz="1200" u="sng" baseline="0">
@@ -10636,7 +10045,7 @@
             <a:rPr lang="pt-BR" sz="1200" baseline="0">
               <a:effectLst/>
             </a:rPr>
-            <a:t>: Quantitativa Discreta.</a:t>
+            <a:t>: Quantitativa Continua.</a:t>
           </a:r>
           <a:endParaRPr lang="pt-BR" sz="1200">
             <a:effectLst/>
@@ -11538,24 +10947,14 @@
         <n v="60"/>
       </sharedItems>
       <fieldGroup base="2">
-        <rangePr startNum="20" endNum="60" groupInterval="3"/>
-        <groupItems count="16">
+        <rangePr startNum="20" endNum="60" groupInterval="10"/>
+        <groupItems count="6">
           <s v="&lt;20"/>
-          <s v="20-22"/>
-          <s v="23-25"/>
-          <s v="26-28"/>
-          <s v="29-31"/>
-          <s v="32-34"/>
-          <s v="35-37"/>
-          <s v="38-40"/>
-          <s v="41-43"/>
-          <s v="44-46"/>
-          <s v="47-49"/>
-          <s v="50-52"/>
-          <s v="53-55"/>
-          <s v="56-58"/>
-          <s v="59-61"/>
-          <s v="&gt;62"/>
+          <s v="20-29"/>
+          <s v="30-39"/>
+          <s v="40-49"/>
+          <s v="50-60"/>
+          <s v="&gt;60"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
@@ -12779,10 +12178,10 @@
     <dataField name="fac" fld="0" subtotal="count" showDataAs="runTotal" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="91">
+    <format dxfId="101">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="90">
+    <format dxfId="100">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12791,26 +12190,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="99">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="98">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="97">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="96">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="85">
+    <format dxfId="95">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="84">
+    <format dxfId="94">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -12821,26 +12220,26 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="83">
+    <format dxfId="93">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="82">
+    <format dxfId="92">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="81">
+    <format dxfId="91">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="80">
+    <format dxfId="90">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="79">
+    <format dxfId="89">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="78">
+    <format dxfId="88">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -12865,7 +12264,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4FB4F66-6C34-4ECE-87A4-EDF2E5329E65}" name="Tabela dinâmica4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Idade">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4FB4F66-6C34-4ECE-87A4-EDF2E5329E65}" name="Tabela dinâmica4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Idade">
   <location ref="A3:D13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -12949,22 +12348,22 @@
     <dataField name="fac" fld="1" subtotal="count" showDataAs="runTotal" baseField="1" baseItem="1"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="77">
+    <format dxfId="87">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="76">
+    <format dxfId="86">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="75">
+    <format dxfId="85">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="74">
+    <format dxfId="84">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="73">
+    <format dxfId="83">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="72">
+    <format dxfId="82">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="3">
@@ -12975,7 +12374,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="81">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12984,16 +12383,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="70">
+    <format dxfId="80">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
+    <format dxfId="79">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="78">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="77">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="9">
@@ -13009,6 +12408,129 @@
           </reference>
         </references>
       </pivotArea>
+    </format>
+    <format dxfId="76">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="75">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E00DA975-3257-4A11-9629-C00D632D610A}" name="Tabela dinâmica6" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Acesso">
+  <location ref="A3:D8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <dataFields count="3">
+    <dataField name="fi" fld="2" subtotal="count" baseField="2" baseItem="0"/>
+    <dataField name="%" fld="2" subtotal="count" showDataAs="percentOfTotal" baseField="2" baseItem="0" numFmtId="10"/>
+    <dataField name="fac" fld="2" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <formats count="10">
+    <format dxfId="74">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="73">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="72">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="71">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="70">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="3">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="69">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="68">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="67">
+      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
     <format dxfId="66">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
@@ -13037,11 +12559,11 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E00DA975-3257-4A11-9629-C00D632D610A}" name="Tabela dinâmica6" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Tempo de Acesso">
-  <location ref="A3:D14" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BE0E042-8626-4FFE-8943-97907EBA2D79}" name="Tabela dinâmica2" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
-    <pivotField showAll="0">
+    <pivotField axis="axisCol" showAll="0">
       <items count="3">
         <item x="1"/>
         <item x="0"/>
@@ -13050,7 +12572,7 @@
     </pivotField>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="17">
+      <items count="11">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -13061,12 +12583,6 @@
         <item x="7"/>
         <item x="8"/>
         <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13074,7 +12590,7 @@
   <rowFields count="1">
     <field x="2"/>
   </rowFields>
-  <rowItems count="11">
+  <rowItems count="8">
     <i>
       <x v="1"/>
     </i>
@@ -13094,124 +12610,103 @@
       <x v="6"/>
     </i>
     <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="14"/>
+      <x v="8"/>
     </i>
     <i t="grand">
       <x/>
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="-2"/>
+    <field x="0"/>
   </colFields>
   <colItems count="3">
     <i>
       <x/>
     </i>
-    <i i="1">
+    <i>
       <x v="1"/>
     </i>
-    <i i="2">
-      <x v="2"/>
+    <i t="grand">
+      <x/>
     </i>
   </colItems>
-  <dataFields count="3">
-    <dataField name="fi" fld="2" subtotal="count" baseField="2" baseItem="0"/>
-    <dataField name="%" fld="2" subtotal="count" showDataAs="percentOfTotal" baseField="2" baseItem="0" numFmtId="10"/>
-    <dataField name="fac" fld="2" subtotal="count" showDataAs="runTotal" baseField="2" baseItem="1"/>
+  <dataFields count="1">
+    <dataField name="Contagem de Tempo de acesso semanal" fld="2" subtotal="count" baseField="2" baseItem="0"/>
   </dataFields>
-  <formats count="12">
-    <format dxfId="64">
+  <formats count="10">
+    <format dxfId="21">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="63">
+    <format dxfId="20">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="19">
+      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="17">
+      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="16">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="61">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="2" count="10">
+          <reference field="2" count="7">
             <x v="1"/>
             <x v="2"/>
             <x v="3"/>
             <x v="4"/>
             <x v="5"/>
             <x v="6"/>
-            <x v="7"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="14"/>
+            <x v="8"/>
           </reference>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="59">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+    <format dxfId="13">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="4294967294" count="3">
+          <reference field="0" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
           </reference>
         </references>
       </pivotArea>
-    </format>
-    <format dxfId="58">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="57">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="56">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="55">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="10">
+    </chartFormat>
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
             <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="7"/>
-            <x v="9"/>
-            <x v="10"/>
-            <x v="14"/>
           </reference>
         </references>
       </pivotArea>
-    </format>
-    <format dxfId="54">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="53">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="3">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -13224,8 +12719,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1545B594-CA1D-4A32-BF6F-7E62AA30F615}" name="Tabela dinâmica9" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Faixa Etária">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1545B594-CA1D-4A32-BF6F-7E62AA30F615}" name="Tabela dinâmica9" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Faixa Etária">
   <location ref="A70:B77" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0">
@@ -13297,7 +12792,7 @@
     <dataField name="Média de Tempo de acesso semanal" fld="2" subtotal="average" baseField="1" baseItem="1"/>
   </dataFields>
   <formats count="17">
-    <format dxfId="16">
+    <format dxfId="38">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="2">
@@ -13307,7 +12802,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="37">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -13316,7 +12811,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="36">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -13325,7 +12820,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="35">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -13334,7 +12829,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="12">
+    <format dxfId="34">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -13343,16 +12838,16 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="33">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="32">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="31">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="6">
@@ -13366,22 +12861,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="7">
+    <format dxfId="29">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="28">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="27">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="25">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="6">
@@ -13395,10 +12890,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -13425,8 +12920,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37DF2522-7781-4C0F-A303-F8F4ED826E28}" name="Tabela dinâmica8" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{37DF2522-7781-4C0F-A303-F8F4ED826E28}" name="Tabela dinâmica8" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A50:D58" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisCol" showAll="0">
@@ -13509,25 +13004,25 @@
     <dataField name="Contagem de Idade" fld="1" subtotal="count" baseField="1" baseItem="0"/>
   </dataFields>
   <formats count="20">
-    <format dxfId="36">
+    <format dxfId="58">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="57">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="56">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="55">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="54">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="31">
+    <format dxfId="53">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="52">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="6">
@@ -13541,38 +13036,38 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="51">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="48">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="25">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="46">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="45">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="44">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="43">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="6">
@@ -13586,17 +13081,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -13638,8 +13133,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FBCDAFB-CFBF-4CE8-9461-A0219692DAF8}" name="Tabela dinâmica5" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1FBCDAFB-CFBF-4CE8-9461-A0219692DAF8}" name="Tabela dinâmica5" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A32:D41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisCol" showAll="0">
@@ -13713,183 +13208,23 @@
     <dataField name="Média de Tempo de acesso semanal" fld="2" subtotal="average" baseField="2" baseItem="1" numFmtId="2"/>
   </dataFields>
   <formats count="6">
-    <format dxfId="38">
+    <format dxfId="64">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="39">
+    <format dxfId="63">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="62">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="61">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="37">
+    <format dxfId="59">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5BE0E042-8626-4FFE-8943-97907EBA2D79}" name="Tabela dinâmica2" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="11">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="8">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Contagem de Tempo de acesso semanal" fld="2" subtotal="count" baseField="2" baseItem="0"/>
-  </dataFields>
-  <formats count="10">
-    <format dxfId="52">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="51">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="49">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="7">
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-            <x v="6"/>
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="45">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="0" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="43">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
   <chartFormats count="2">
@@ -14590,9 +13925,9 @@
   <dimension ref="A3:D27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="2.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14612,155 +13947,73 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B4" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C4" s="11">
-        <v>0.13333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="D4" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B5" s="10">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C5" s="11">
-        <v>6.6666666666666666E-2</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="D5" s="10">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B6" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6" s="11">
-        <v>0.1</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="D6" s="10">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B7" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C7" s="11">
-        <v>0.23333333333333334</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="D7" s="10">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8" s="10">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11">
-        <v>6.6666666666666666E-2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="11">
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="D9" s="10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B10" s="10">
-        <v>6</v>
-      </c>
-      <c r="C10" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="10">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="10">
-        <v>2</v>
-      </c>
-      <c r="C11" s="11">
-        <v>6.6666666666666666E-2</v>
-      </c>
-      <c r="D11" s="10">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="10">
-        <v>1</v>
-      </c>
-      <c r="C12" s="11">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="D12" s="10">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="10">
-        <v>1</v>
-      </c>
-      <c r="C13" s="11">
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="D13" s="10">
         <v>30</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="10">
-        <v>30</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="10"/>
     </row>
     <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
@@ -14772,91 +14025,67 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="B17" s="10">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="B18" s="10">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="B19" s="10">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="B20" s="10">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="10">
-        <v>2</v>
+    <row r="21" spans="1:2" ht="13" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="14">
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B22" s="10">
-        <v>2</v>
-      </c>
+      <c r="A22" s="9"/>
+      <c r="B22" s="10"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="10">
-        <v>6</v>
-      </c>
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="10">
-        <v>2</v>
-      </c>
+      <c r="A24" s="9"/>
+      <c r="B24" s="10"/>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="10">
-        <v>1</v>
-      </c>
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="10">
-        <v>1</v>
-      </c>
+      <c r="A26" s="9"/>
+      <c r="B26" s="10"/>
     </row>
     <row r="27" spans="1:2" ht="13" x14ac:dyDescent="0.25">
-      <c r="A27" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="14">
-        <v>30</v>
-      </c>
+      <c r="A27" s="13"/>
+      <c r="B27" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -14878,24 +14107,24 @@
   <sheetData>
     <row r="2" spans="1:7" ht="13" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:7" ht="13" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>51</v>
+      <c r="A3" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="F3" s="29">
+      <c r="F3" s="28">
         <v>6</v>
       </c>
       <c r="G3" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>42</v>
+      <c r="A4" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>2</v>
@@ -14906,183 +14135,183 @@
       <c r="D4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="32" t="s">
-        <v>55</v>
+      <c r="G4" s="33" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="28">
+        <v>34</v>
+      </c>
+      <c r="B5" s="27">
         <v>3</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <v>2</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="27">
         <v>5</v>
       </c>
-      <c r="G5" s="32"/>
+      <c r="G5" s="33"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="28">
+        <v>35</v>
+      </c>
+      <c r="B6" s="27">
         <v>1</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="27">
         <v>3</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="27">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="28">
+        <v>36</v>
+      </c>
+      <c r="B7" s="27">
         <v>3</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>6</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="28">
+        <v>37</v>
+      </c>
+      <c r="B8" s="27">
         <v>3</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <v>1</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <v>4</v>
       </c>
-      <c r="G8" s="32" t="s">
-        <v>65</v>
+      <c r="G8" s="33" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="28">
+        <v>38</v>
+      </c>
+      <c r="B9" s="27">
         <v>3</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>3</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>6</v>
       </c>
-      <c r="G9" s="32"/>
+      <c r="G9" s="33"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28">
+        <v>39</v>
+      </c>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27">
         <v>1</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28">
+        <v>40</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27">
         <v>1</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="27">
         <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <v>13</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <v>17</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="27">
         <v>30</v>
       </c>
-      <c r="G12" s="32" t="s">
-        <v>64</v>
+      <c r="G12" s="33" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G13" s="32"/>
+      <c r="G13" s="33"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G14" s="32"/>
+      <c r="G14" s="33"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G16" s="31" t="s">
-        <v>66</v>
+      <c r="G16" s="30" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="32" t="s">
-        <v>68</v>
+      <c r="G17" s="33" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="32"/>
+      <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="32"/>
+      <c r="G19" s="33"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="34" t="s">
-        <v>69</v>
+      <c r="G21" s="32" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="32" t="s">
-        <v>70</v>
+      <c r="G22" s="33" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="32"/>
+      <c r="G23" s="33"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="32"/>
+      <c r="G24" s="33"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="B32" s="27" t="s">
-        <v>51</v>
+      <c r="A32" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>41</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
-        <v>42</v>
+      <c r="A33" s="26" t="s">
+        <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>2</v>
@@ -15096,95 +14325,95 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B34" s="30">
+        <v>34</v>
+      </c>
+      <c r="B34" s="29">
         <v>22</v>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="29">
         <v>20.5</v>
       </c>
-      <c r="D34" s="30">
+      <c r="D34" s="29">
         <v>21.4</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35" s="30">
+        <v>35</v>
+      </c>
+      <c r="B35" s="29">
         <v>25</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="29">
         <v>26.666666666666668</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="29">
         <v>26.25</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" s="30">
+        <v>36</v>
+      </c>
+      <c r="B36" s="29">
         <v>30</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="29">
         <v>31</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="29">
         <v>30.666666666666668</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B37" s="30">
+        <v>37</v>
+      </c>
+      <c r="B37" s="29">
         <v>36.333333333333336</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="29">
         <v>38</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="29">
         <v>36.75</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="B38" s="30">
+        <v>38</v>
+      </c>
+      <c r="B38" s="29">
         <v>42.666666666666664</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="29">
         <v>40</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="29">
         <v>41.333333333333336</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30">
+        <v>39</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29">
         <v>48</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="29">
         <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30">
+        <v>40</v>
+      </c>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29">
         <v>60</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40" s="29">
         <v>60</v>
       </c>
     </row>
@@ -15192,29 +14421,29 @@
       <c r="A41" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>32.153846153846153</v>
       </c>
-      <c r="C41" s="30">
+      <c r="C41" s="29">
         <v>33.705882352941174</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41" s="29">
         <v>33.033333333333331</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>2</v>
@@ -15228,7 +14457,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B52" s="10">
         <v>4</v>
@@ -15242,7 +14471,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B53" s="10">
         <v>2</v>
@@ -15256,7 +14485,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B54" s="10">
         <v>2</v>
@@ -15270,7 +14499,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B55" s="10"/>
       <c r="C55" s="10">
@@ -15282,7 +14511,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B56" s="10">
         <v>4</v>
@@ -15296,7 +14525,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B57" s="10">
         <v>1</v>
@@ -15324,57 +14553,57 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B71" s="33">
+        <v>48</v>
+      </c>
+      <c r="B71" s="31">
         <v>23.125</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="B72" s="33">
+        <v>49</v>
+      </c>
+      <c r="B72" s="31">
         <v>31</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B73" s="33">
+        <v>50</v>
+      </c>
+      <c r="B73" s="31">
         <v>34.5</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B74" s="33">
+        <v>51</v>
+      </c>
+      <c r="B74" s="31">
         <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B75" s="33">
+        <v>52</v>
+      </c>
+      <c r="B75" s="31">
         <v>38.666666666666664</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B76" s="33">
+        <v>53</v>
+      </c>
+      <c r="B76" s="31">
         <v>49.333333333333336</v>
       </c>
     </row>
@@ -15746,7 +14975,7 @@
         <v>44</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F28" s="17">
         <f>AVERAGE(B2:B31)</f>
@@ -15768,7 +14997,7 @@
         <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F29" s="17" cm="1">
         <f t="array" ref="F29:F31">_xlfn.MODE.MULT(B2:B31)</f>
@@ -15816,7 +15045,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="E32" s="19" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="F32" s="17">
         <f>MEDIAN(B2:B31)</f>
@@ -15829,7 +15058,7 @@
     </row>
     <row r="33" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E33" s="19" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F33" s="17">
         <f>_xlfn.VAR.S(B2:B31)</f>
@@ -15842,7 +15071,7 @@
     </row>
     <row r="34" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E34" s="19" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F34" s="17">
         <f>_xlfn.STDEV.S(B2:B31)</f>
@@ -15855,13 +15084,13 @@
     </row>
     <row r="35" spans="5:11" x14ac:dyDescent="0.25">
       <c r="E35" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="26">
+        <v>24</v>
+      </c>
+      <c r="F35" s="25">
         <f>F34/F28 * 100</f>
         <v>37.401524465876648</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="25">
         <f>G34/G28*100</f>
         <v>27.476008769514102</v>
       </c>
@@ -15872,7 +15101,7 @@
     </row>
     <row r="38" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J38" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K38" s="2">
         <v>12</v>
@@ -15880,7 +15109,7 @@
     </row>
     <row r="39" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J39" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K39" s="2">
         <v>15.75</v>
@@ -15888,7 +15117,7 @@
     </row>
     <row r="40" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J40" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K40" s="2">
         <v>20.5</v>
@@ -15896,7 +15125,7 @@
     </row>
     <row r="41" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J41" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K41" s="2">
         <v>32.5</v>
@@ -15904,7 +15133,7 @@
     </row>
     <row r="42" spans="5:11" x14ac:dyDescent="0.25">
       <c r="J42" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K42" s="2">
         <v>40</v>
@@ -15912,7 +15141,7 @@
     </row>
     <row r="55" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J55" s="2" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K55" s="2">
         <v>20</v>
@@ -15920,7 +15149,7 @@
     </row>
     <row r="56" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J56" s="2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="K56" s="2">
         <v>26.75</v>
@@ -15928,7 +15157,7 @@
     </row>
     <row r="57" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J57" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K57" s="2">
         <v>30</v>
@@ -15936,7 +15165,7 @@
     </row>
     <row r="58" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J58" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="K58" s="2">
         <v>40</v>
@@ -15944,7 +15173,7 @@
     </row>
     <row r="59" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J59" s="2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="K59" s="2">
         <v>48</v>
@@ -15956,14 +15185,14 @@
     </row>
     <row r="61" spans="10:12" x14ac:dyDescent="0.25">
       <c r="J61" s="2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K61" s="25">
-        <f>STANDARDIZE(K59,G28,G34)</f>
-        <v>1.6489938662283201</v>
+        <f>STANDARDIZE(60,G28,G34)</f>
+        <v>2.9711270329147235</v>
       </c>
       <c r="L61" s="16" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
